--- a/public/sap-reporting/expansion-150-downloads/EXT-PP09-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-PP09-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Ra6751697855e4c1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R98d1809032dc41a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R04a3b9ba358a4de2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rf4e17efe50804aac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rcf2f6c14b1b24f96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rbb87d95362f6438f"/>
   </x:sheets>
 </x:workbook>
 </file>
